--- a/ma_so_thue_doanh_nghiep.xlsx
+++ b/ma_so_thue_doanh_nghiep.xlsx
@@ -448,63 +448,63 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3900583134</t>
+          <t>2902228006</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DOANH NGHIỆP TƯ NHÂN DUNG PHƯƠNG</t>
+          <t>CÔNG TY TNHH DŨNG PHƯƠNG NA</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>11/2009</t>
+          <t>06/2025</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>6001580837</t>
+          <t>4900924121</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN DƯỢC AVISPHARM BMT</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN THƯƠNG MẠI DỊCH VỤ NGUYỄN THƠM</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>08/2017</t>
+          <t>06/2025</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0315890268</t>
+          <t>3604023679</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH 3S SOLUTION</t>
+          <t>CÔNG TY TNHH TRÁI CÂY VINH QUANG</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>09/2019</t>
+          <t>06/2025</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0111081678</t>
+          <t>0318995861</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH PHỤ TÙNG Ô TÔ HẢI ĐĂNG</t>
+          <t>CÔNG TY TNHH MTV VĂN SANG</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -516,12 +516,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0318992028</t>
+          <t>4900924097</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH VĂN PHÒNG PHẨM BẢO VY</t>
+          <t>CÔNG TY TNHH VẬN TẢI QUỐC TẾ LONG SƠN</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -533,12 +533,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0111082495</t>
+          <t>0111083234</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH TM &amp; XNK THANH PHÁT</t>
+          <t>CÔNG TY TNHH PHOVERON</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -550,12 +550,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0318993617</t>
+          <t>6001794010</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỈM CƯỜI</t>
+          <t>CÔNG TY TNHH SẢN XUẤT THƯƠNG MẠI VIỆT ĐỨC PHÁT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -567,12 +567,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0318993430</t>
+          <t>2401023583</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ NHÀ Ở HOÀNG PHÁT</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI ĐẦU TƯ XD KIM THỊNH PHÁT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -584,12 +584,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0111081558</t>
+          <t>6300380956</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH PHÁT TRIỂN DỊCH VỤ VÀ THƯƠNG MẠI MINH TRƯỜNG</t>
+          <t>CÔNG TY TNHH NGỌC TRƯỜNG PHÁT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -601,12 +601,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0111081082</t>
+          <t>4900924107</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH DỊCH VỤ CUNG ỨNG ANH MINH</t>
+          <t>CÔNG TY TNHH THIỆP VÂN</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -618,12 +618,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0111081251</t>
+          <t>1201700451</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MARKET NGÂN HÀ XANH</t>
+          <t>CÔNG TY TNHH MTV PHÁT TIẾN TOWER</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -635,46 +635,46 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0305601982</t>
+          <t>2401024001</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ THƯƠNG MẠI GOLDENSTAR</t>
+          <t>CÔNG TY TNHH KINH DOANH TỔNG HỢP NGUYỄN THÀNH CÔNG</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>04/2008</t>
+          <t>06/2025</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0111082382</t>
+          <t>0315043039</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ THỂ THAO THÀNH DANH</t>
+          <t>CÔNG TY TNHH LOTTO VIỆT NAM</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>06/2025</t>
+          <t>05/2018</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0111082336</t>
+          <t>0318995815</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH TRUYỀN THÔNG GIẢI TRÍ VÀ ĐÀO TẠO NGHỆ THUẬT HANA</t>
+          <t>CÔNG TY TNHH SỬA CHỮA CƠ KHÍ LẬP THÀNH</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -686,12 +686,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0111081861</t>
+          <t>2001385934</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ KỸ THUẬT THÁI SƠN</t>
+          <t>CÔNG TY TNHH MTV PHÚC THỊNH 3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -703,12 +703,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0111081808</t>
+          <t>2902228038</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH TRIỆU NGUYỆT CÁT</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI ĐĂNG KHÔI TB</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -720,12 +720,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1102099896</t>
+          <t>0111083280</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH DỆT KIM MINH TÂN</t>
+          <t>CÔNG TY TNHH SẢN XUẤT THỰC PHẨM TÔ GIA</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -737,12 +737,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0111081660</t>
+          <t>3604022795</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI DIGIART</t>
+          <t>CÔNG TY TNHH CƠ KHÍ YANQI VIỆT NAM</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -754,12 +754,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0111082696</t>
+          <t>6001793987</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI TIỆP DUNG</t>
+          <t>CÔNG TY TNHH CENTER VENTURES</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -771,12 +771,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0318992606</t>
+          <t>0318990302</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH CÔNG NGHỆ SẢN XUẤT PHƯƠNG LINH</t>
+          <t>CÔNG TY TNHH TMDV CƠ KHÍ QUỐC DŨNG</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -788,12 +788,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0202290728</t>
+          <t>3703339257</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI THỰC PHẨM XANH ĐOÀN PHÁT</t>
+          <t>CÔNG TY TNHH TMDV TRẦN HƯNG PHÁT</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -805,12 +805,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0202290622</t>
+          <t>0318989843</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH LOVE HOME THUÂN LOAN</t>
+          <t>CÔNG TY TNHH MTV TMDV LÊ TUẤN TÚ</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -822,12 +822,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1402207334</t>
+          <t>4800941860</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XÂY DỰNG THIẾT KẾ THI CÔNG AN THỊNH</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI QUÂN VÂN 88</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -839,29 +839,29 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0700210210-002</t>
+          <t>0111081452</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>VĂN PHÒNG ĐẠI DIỆN CÔNG TY CỔ PHẦN ĐẦU TƯ VÀ XÂY LẮP TRƯỜNG SƠN</t>
+          <t>CÔNG TY TNHH MTV ĐẦU TƯ PHÁT TRIỂN THƯƠNG MẠI &amp; DỊCH VỤ THANH TÙNG</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>01/2015</t>
+          <t>06/2025</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0318991916</t>
+          <t>0700897931</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH JH GROUP COMPANY</t>
+          <t>CÔNG TY TNHH TM ĐỨC LONG</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0318991225</t>
+          <t>0111079358</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH NHÀ HÀNG THIÊN QUẾ</t>
+          <t>CÔNG TY TNHH PHÁT TRIỂN ĐẦU TƯ THƯƠNG MẠI VÀ XÂY DỰNG MINH ĐẠT</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -890,12 +890,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0318991465</t>
+          <t>1201700444</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THIẾT BỊ CÔNG NGHỆ HÂN LONG</t>
+          <t>CÔNG TY TNHH ĐÓNG TÀU SÔNG TIỀN</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -907,12 +907,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0111068927</t>
+          <t>1001301234</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN PHÁT TRIỂN KHU CÔNG NGHIỆP C.E.O</t>
+          <t>CÔNG TY TNHH SẢN XUẤT MAY MẶC MINH LONG</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -924,12 +924,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0318991810</t>
+          <t>1102099769</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ TỊNH THƯ</t>
+          <t>CÔNG TY TNHH TMDV MELIAN TOUR</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -941,12 +941,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0318979281</t>
+          <t>2301338445</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH ZHEJIANG KANGBEIDE SMART HOME</t>
+          <t>CÔNG TY TNHH SẢN XUẤT DỊCH VỤ VÀ THƯƠNG MẠI THÀNH ĐẠT</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -958,12 +958,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0318992684</t>
+          <t>3703339264</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN PROBIZ HUB</t>
+          <t>CÔNG TY CỔ PHẦN NASAGA VIỆT NAM</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -975,12 +975,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0402278647</t>
+          <t>2301338420</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN BRALY ĐÀ NẴNG</t>
+          <t>CÔNG TY TNHH SẢN XUẤT VÀ KINH DOANH GIẤY MINH ANH</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -992,12 +992,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0402278340</t>
+          <t>4601637376</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH DU LỊCH VẬN TẢI NGUYÊN KHÁNH</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ ĐỊNH HUYỀN AUTO</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1009,12 +1009,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0111082343</t>
+          <t>0111080353</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH ĐẦU TƯ THƯƠNG MẠI &amp; XÂY DỰNG MLA</t>
+          <t>CÔNG TY TNHH TNS VIỆT NAM LAND</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1026,12 +1026,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2401022910</t>
+          <t>3502548846</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ ĐIỆN MÁY TRUNG NGUYÊN</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ MD VŨNG TÀU</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1043,12 +1043,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0111081318</t>
+          <t>1001301227</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH DỊCH VỤ VÀ THƯƠNG MẠI HƯƠNG LINH GIANG</t>
+          <t>CÔNG TY TNHH TMDV ĐẠI VŨ</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1060,12 +1060,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2401022903</t>
+          <t>5100504666</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH LINH KIỆN THIẾT BỊ TỰ ĐỘNG THÀNH ĐẠT</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI HIỀN TIẾN HÀ GIANG</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1077,12 +1077,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0111081903</t>
+          <t>0111079534</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH TRÀ SEN HÀ NỘI</t>
+          <t>CÔNG TY TNHH SẢN XUẤT THƯƠNG MẠI VÀ DỊCH VỤ BẾP NGUYÊN KHÔI</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1094,12 +1094,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>3801319139</t>
+          <t>0318995773</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI QUỐC TẾ VIỆT CAM</t>
+          <t>CÔNG TY TNHH LUNG NGUYỆT</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1111,12 +1111,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2001385691</t>
+          <t>6001794074</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THỦY LINH CÀ MAU</t>
+          <t>CÔNG TY TNHH ĐỨC THẮNG BAN MÊ</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1128,12 +1128,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0111081879</t>
+          <t>3703339271</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ THÀNH ĐẠT GLOBAL</t>
+          <t>CÔNG TY TNHH MTV VẬN TẢI TM VÀ DV THANH HÀ</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1145,12 +1145,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2001385684</t>
+          <t>3502548839</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH SOĐO LAND</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ DU LỊCH PHÚC HOÀNG</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1162,12 +1162,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0111081935</t>
+          <t>0111080152</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN MINH ANH GROUP</t>
+          <t>CÔNG TY TNHH ĐẦU TƯ VÀ PHÁT TRIỂN BÌNH MINH TK</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1179,12 +1179,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3002291102</t>
+          <t>0111078178</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH DỊCH VỤ VẬN TẢI LÊ CƯỜNG</t>
+          <t>CÔNG TY TNHH CMC THANH BÌNH</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1196,12 +1196,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>5400556009</t>
+          <t>0318994307</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH TM VÀ DV HÙNG NGUYÊN</t>
+          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI ĐẦU TƯ &amp; LOGISTICS AN PHÁT</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1213,12 +1213,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0111082664</t>
+          <t>1201700684</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ DIGITAL XUÂN KHÁNH</t>
+          <t>CÔNG TY TNHH VÀNG BẠC TÁM TUÔI</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1230,12 +1230,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>5400555975</t>
+          <t>4601637383</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN DỊCH VỤ THƯƠNG MẠI DUY MẠNH</t>
+          <t>CÔNG TY TNHH CUNG ỨNG NGUỒN NHÂN LỰC VN</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1247,12 +1247,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0318993568</t>
+          <t>0111079069</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN TƯ VĂN</t>
+          <t>CÔNG TY CỔ PHẦN CHUYỂN ĐỔI XANH MIỀN BẮC</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1264,12 +1264,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>5400555950</t>
+          <t>0901191938</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN GẠCH HÒA BÌNH</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ QUANG DỰ</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1281,17 +1281,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2400839883</t>
+          <t>3502548821</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>VĂN PHÒNG CÔNG CHỨNG NGUYỄN THỊ YẾN</t>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ VÀ PHÁT TRIỂN DU LỊCH BHN VŨNG TÀU</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>05/2018</t>
+          <t>06/2025</t>
         </is>
       </c>
     </row>
